--- a/etf_holdings/2026-09-03_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-03_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV8"/>
+  <dimension ref="A1:CF11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -739,50 +739,100 @@
       </c>
       <c r="BM1" t="inlineStr">
         <is>
+          <t>00407A_異動類型</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>00407A_調整方向</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>00407A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>00407A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>00407A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>00407A_權重_今日</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>00407A_權重變化</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>00407A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>00407A_股數_今日</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>00407A_股數變化</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
           <t>00993A_異動類型</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>00993A_調整方向</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>00993A_權重_昨日</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>00993A_權重_今日</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>00993A_權重變化</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>00993A_股數_昨日</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>00993A_股數_今日</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>00993A_股數變化</t>
         </is>
@@ -800,11 +850,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00980A,00985A,00993A</t>
+          <t>00407A,00980A,00985A,00993A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -961,26 +1011,72 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
+          <t>5.72%</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>5.87%</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="BT2" t="n">
+        <v>195000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>581644</v>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>386,644</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>3.49%</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>3.58%</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>+0.09%</t>
         </is>
       </c>
-      <c r="BT2" t="n">
+      <c r="CD2" t="n">
         <v>47000</v>
       </c>
-      <c r="BU2" t="n">
+      <c r="CE2" t="n">
         <v>140191</v>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>93,191</t>
         </is>
@@ -1119,48 +1215,58 @@
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr">
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>南電</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>南電</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>2.52%</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>2.17%</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>-0.35%</t>
         </is>
       </c>
-      <c r="BT3" t="n">
+      <c r="CD3" t="n">
         <v>216000</v>
       </c>
-      <c r="BU3" t="n">
+      <c r="CE3" t="n">
         <v>185000</v>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>-31,000</t>
         </is>
@@ -1281,48 +1387,58 @@
           <t>-30,000</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>川湖</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>川湖</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>4.04%</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>3.80%</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>-0.24%</t>
         </is>
       </c>
-      <c r="BT4" t="n">
+      <c r="CD4" t="n">
         <v>30000</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="CE4" t="n">
         <v>28000</v>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>-2,000</t>
         </is>
@@ -1331,12 +1447,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1344,55 +1460,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00981A,00993A</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.61%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.09%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-0.52%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>1457000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>219000</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-1,238,000</t>
-        </is>
-      </c>
+          <t>00407A,00993A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -1450,55 +1530,101 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="BT5" t="n">
-        <v>113000</v>
+        <v>2045000</v>
       </c>
       <c r="BU5" t="n">
-        <v>198000</v>
+        <v>1000000</v>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>-1,045,000</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="CD5" t="n">
+        <v>1338000</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>1276000</v>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>-62,000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1506,19 +1632,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00982A,00993A</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-0.52%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1457000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>219000</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-1,238,000</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -1529,52 +1691,16 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1.22%</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1.39%</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>+0.17%</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>3404000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3704000</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>300,000</t>
-        </is>
-      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
@@ -1605,62 +1731,72 @@
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr">
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>1.06%</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>1.70%</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>+0.64%</t>
-        </is>
-      </c>
-      <c r="BT6" t="n">
-        <v>611000</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>939000</v>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>328,000</t>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2.28%</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>+0.96%</t>
+        </is>
+      </c>
+      <c r="CD6" t="n">
+        <v>113000</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>198000</v>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>85,000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1668,55 +1804,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00981A,00993A</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4.90%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>4.95%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>2397000</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2427000</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>30,000</t>
-        </is>
-      </c>
+          <t>00407A,00993A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -1774,55 +1874,101 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="BT7" t="n">
-        <v>29000</v>
+        <v>55000</v>
       </c>
       <c r="BU7" t="n">
-        <v>23000</v>
+        <v>80000</v>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>25,000</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>+0.97%</t>
+        </is>
+      </c>
+      <c r="CD7" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>25000</v>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>12,000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1830,7 +1976,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00403A,00993A</t>
+          <t>00982A,00993A</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1853,42 +1999,60 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>1.39%</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>3404000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3704000</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>300,000</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="n">
-        <v>1000</v>
-      </c>
+      <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
@@ -1911,50 +2075,558 @@
       <c r="BJ8" t="inlineStr"/>
       <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr">
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>+0.64%</t>
+        </is>
+      </c>
+      <c r="CD8" t="n">
+        <v>611000</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>939000</v>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>328,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4.90%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4.95%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2397000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2427000</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="CD9" t="n">
+        <v>29000</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>23000</v>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>-6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>臻鼎-KY</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00403A,00993A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>臻鼎-KY</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
         <is>
           <t>0.87%</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>1.93%</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>+1.06%</t>
         </is>
       </c>
-      <c r="BT8" t="n">
+      <c r="CD10" t="n">
         <v>171000</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CE10" t="n">
         <v>390000</v>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>219,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00407A,00993A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>1.72%</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>+0.74%</t>
+        </is>
+      </c>
+      <c r="BT11" t="n">
+        <v>221000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>351000</v>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>130,000</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>+0.59%</t>
+        </is>
+      </c>
+      <c r="CD11" t="n">
+        <v>82000</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>122000</v>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>40,000</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-09-03_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-03_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF11"/>
+  <dimension ref="A1:BV13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,200 +639,150 @@
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>00985A_異動類型</t>
+          <t>00990A_異動類型</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>00985A_調整方向</t>
+          <t>00990A_調整方向</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>00985A_股票名稱_昨日</t>
+          <t>00990A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>00985A_股票名稱_今日</t>
+          <t>00990A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>00985A_權重_昨日</t>
+          <t>00990A_權重_昨日</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>00985A_權重_今日</t>
+          <t>00990A_權重_今日</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>00985A_權重變化</t>
+          <t>00990A_權重變化</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>00985A_股數_昨日</t>
+          <t>00990A_股數_昨日</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>00985A_股數_今日</t>
+          <t>00990A_股數_今日</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>00985A_股數變化</t>
+          <t>00990A_股數變化</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>00992A_異動類型</t>
+          <t>00407A_異動類型</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>00992A_調整方向</t>
+          <t>00407A_調整方向</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>00992A_股票名稱_昨日</t>
+          <t>00407A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>00992A_股票名稱_今日</t>
+          <t>00407A_股票名稱_今日</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>00992A_權重_昨日</t>
+          <t>00407A_權重_昨日</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>00992A_權重_今日</t>
+          <t>00407A_權重_今日</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>00992A_權重變化</t>
+          <t>00407A_權重變化</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>00992A_股數_昨日</t>
+          <t>00407A_股數_昨日</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>00992A_股數_今日</t>
+          <t>00407A_股數_今日</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>00992A_股數變化</t>
+          <t>00407A_股數變化</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>00407A_異動類型</t>
+          <t>00993A_異動類型</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>00407A_調整方向</t>
+          <t>00993A_調整方向</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>00407A_股票名稱_昨日</t>
+          <t>00993A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>00407A_股票名稱_今日</t>
+          <t>00993A_股票名稱_今日</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>00407A_權重_昨日</t>
+          <t>00993A_權重_昨日</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>00407A_權重_今日</t>
+          <t>00993A_權重_今日</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>00407A_權重變化</t>
+          <t>00993A_權重變化</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>00407A_股數_昨日</t>
+          <t>00993A_股數_昨日</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>00407A_股數_今日</t>
+          <t>00993A_股數_今日</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
-        <is>
-          <t>00407A_股數變化</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>00993A_異動類型</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>00993A_調整方向</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>00993A_股票名稱_昨日</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>00993A_股票名稱_今日</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>00993A_權重_昨日</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>00993A_權重_今日</t>
-        </is>
-      </c>
-      <c r="CC1" t="inlineStr">
-        <is>
-          <t>00993A_權重變化</t>
-        </is>
-      </c>
-      <c r="CD1" t="inlineStr">
-        <is>
-          <t>00993A_股數_昨日</t>
-        </is>
-      </c>
-      <c r="CE1" t="inlineStr">
-        <is>
-          <t>00993A_股數_今日</t>
-        </is>
-      </c>
-      <c r="CF1" t="inlineStr">
         <is>
           <t>00993A_股數變化</t>
         </is>
@@ -850,11 +800,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00407A,00980A,00985A,00993A</t>
+          <t>00407A,00980A,00993A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -933,62 +883,62 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr">
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>緯穎科技服務</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>緯穎科技服務</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>4.11%</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4.16%</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>56000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>167036</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>111,036</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>5.72%</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>5.87%</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="BJ2" t="n">
+        <v>195000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>581644</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>386,644</t>
+        </is>
+      </c>
       <c r="BM2" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -1011,72 +961,26 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>5.72%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="BT2" t="n">
-        <v>195000</v>
+        <v>47000</v>
       </c>
       <c r="BU2" t="n">
-        <v>581644</v>
+        <v>140191</v>
       </c>
       <c r="BV2" t="inlineStr">
-        <is>
-          <t>386,644</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>3.49%</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>3.58%</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>+0.09%</t>
-        </is>
-      </c>
-      <c r="CD2" t="n">
-        <v>47000</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>140191</v>
-      </c>
-      <c r="CF2" t="inlineStr">
         <is>
           <t>93,191</t>
         </is>
@@ -1215,58 +1119,48 @@
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>南電</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>南電</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>2.52%</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>2.17%</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>-0.35%</t>
         </is>
       </c>
-      <c r="CD3" t="n">
+      <c r="BT3" t="n">
         <v>216000</v>
       </c>
-      <c r="CE3" t="n">
+      <c r="BU3" t="n">
         <v>185000</v>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>-31,000</t>
         </is>
@@ -1275,12 +1169,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1288,7 +1182,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00992A,00993A</t>
+          <t>00407A,00993A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1353,106 +1247,96 @@
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>7.61%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>6.69%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>235000</v>
+        <v>2045000</v>
       </c>
       <c r="BK4" t="n">
-        <v>205000</v>
+        <v>1000000</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>-30,000</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr">
+          <t>-1,045,000</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>4.04%</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>3.80%</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>-0.24%</t>
-        </is>
-      </c>
-      <c r="CD4" t="n">
-        <v>30000</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>28000</v>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>-2,000</t>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="BT4" t="n">
+        <v>1338000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1276000</v>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>-62,000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1460,19 +1344,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-0.52%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1457000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>219000</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-1,238,000</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -1530,101 +1450,55 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="BT5" t="n">
-        <v>2045000</v>
+        <v>113000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1000000</v>
+        <v>198000</v>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>-1,045,000</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>1.69%</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>1.57%</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>-0.12%</t>
-        </is>
-      </c>
-      <c r="CD5" t="n">
-        <v>1338000</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>1276000</v>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>-62,000</t>
+          <t>85,000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1632,55 +1506,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00981A,00993A</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.61%</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.09%</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-0.52%</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>1457000</v>
-      </c>
-      <c r="M6" t="n">
-        <v>219000</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-1,238,000</t>
-        </is>
-      </c>
+          <t>00990A,00993A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -1711,16 +1549,52 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.28%</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>+0.58%</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1008000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1665000</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>657,000</t>
+        </is>
+      </c>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="inlineStr"/>
@@ -1731,60 +1605,50 @@
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>金像電子</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>金像電子</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>1.32%</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2.28%</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>+0.96%</t>
-        </is>
-      </c>
-      <c r="CD6" t="n">
-        <v>113000</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>198000</v>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>85,000</t>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="BT6" t="n">
+        <v>59000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>131000</v>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>72,000</t>
         </is>
       </c>
     </row>
@@ -1857,16 +1721,52 @@
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>+0.85%</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>55000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>80000</v>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
       <c r="BM7" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -1879,82 +1779,36 @@
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="BT7" t="n">
-        <v>55000</v>
+        <v>13000</v>
       </c>
       <c r="BU7" t="n">
-        <v>80000</v>
+        <v>25000</v>
       </c>
       <c r="BV7" t="inlineStr">
-        <is>
-          <t>25,000</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>大立光電</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>大立光電</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>0.94%</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>1.91%</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>+0.97%</t>
-        </is>
-      </c>
-      <c r="CD7" t="n">
-        <v>13000</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>25000</v>
-      </c>
-      <c r="CF7" t="inlineStr">
         <is>
           <t>12,000</t>
         </is>
@@ -1963,12 +1817,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1976,7 +1830,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00982A,00993A</t>
+          <t>00990A,00993A</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1999,52 +1853,16 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1.22%</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>1.39%</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>+0.17%</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>3404000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3704000</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>300,000</t>
-        </is>
-      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
@@ -2055,15 +1873,33 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
       <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
       <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>158000</v>
+      </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
@@ -2075,72 +1911,62 @@
       <c r="BJ8" t="inlineStr"/>
       <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
-      <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr"/>
-      <c r="BR8" t="inlineStr"/>
-      <c r="BS8" t="inlineStr"/>
-      <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr"/>
-      <c r="BV8" t="inlineStr"/>
-      <c r="BW8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>1.06%</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>1.70%</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>+0.64%</t>
-        </is>
-      </c>
-      <c r="CD8" t="n">
-        <v>611000</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>939000</v>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>328,000</t>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>4.34%</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>-0.88%</t>
+        </is>
+      </c>
+      <c r="BT8" t="n">
+        <v>134000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>107000</v>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>-27,000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2148,55 +1974,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00981A,00993A</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4.90%</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>4.95%</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>2397000</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2427000</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>30,000</t>
-        </is>
-      </c>
+          <t>00982A,00993A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -2207,16 +1997,52 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1.39%</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>3404000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3704000</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>300,000</t>
+        </is>
+      </c>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
@@ -2247,72 +2073,62 @@
       <c r="BJ9" t="inlineStr"/>
       <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>1.62%</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>1.30%</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>-0.32%</t>
-        </is>
-      </c>
-      <c r="CD9" t="n">
-        <v>29000</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>23000</v>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>-6,000</t>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>+0.64%</t>
+        </is>
+      </c>
+      <c r="BT9" t="n">
+        <v>611000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>939000</v>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>328,000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2320,19 +2136,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00403A,00993A</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4.90%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4.95%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>2397000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2427000</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -2353,32 +2205,14 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="n">
-        <v>1000</v>
-      </c>
+      <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
@@ -2401,72 +2235,62 @@
       <c r="BJ10" t="inlineStr"/>
       <c r="BK10" t="inlineStr"/>
       <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
-      <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
-      <c r="BQ10" t="inlineStr"/>
-      <c r="BR10" t="inlineStr"/>
-      <c r="BS10" t="inlineStr"/>
-      <c r="BT10" t="inlineStr"/>
-      <c r="BU10" t="inlineStr"/>
-      <c r="BV10" t="inlineStr"/>
-      <c r="BW10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>0.87%</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>1.93%</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>+1.06%</t>
-        </is>
-      </c>
-      <c r="CD10" t="n">
-        <v>171000</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>390000</v>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>219,000</t>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="BT10" t="n">
+        <v>29000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>23000</v>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>-6,000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2474,7 +2298,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
+          <t>00990A,00993A</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -2517,15 +2341,33 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
       <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
       <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
+      <c r="BA11" t="n">
+        <v>94000</v>
+      </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
@@ -2549,82 +2391,342 @@
       </c>
       <c r="BO11" t="inlineStr">
         <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>2.12%</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="BT11" t="n">
+        <v>90000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>100000</v>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00403A,00993A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>+1.06%</t>
+        </is>
+      </c>
+      <c r="BT12" t="n">
+        <v>171000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>390000</v>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>219,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00407A,00993A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
         <is>
           <t>0.98%</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BH13" t="inlineStr">
         <is>
           <t>1.72%</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BI13" t="inlineStr">
         <is>
           <t>+0.74%</t>
         </is>
       </c>
-      <c r="BT11" t="n">
+      <c r="BJ13" t="n">
         <v>221000</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="BK13" t="n">
         <v>351000</v>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BL13" t="inlineStr">
         <is>
           <t>130,000</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BM13" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="BN13" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="BO13" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="BP13" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="BQ13" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="BR13" t="inlineStr">
         <is>
           <t>1.51%</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="BS13" t="inlineStr">
         <is>
           <t>+0.59%</t>
         </is>
       </c>
-      <c r="CD11" t="n">
+      <c r="BT13" t="n">
         <v>82000</v>
       </c>
-      <c r="CE11" t="n">
+      <c r="BU13" t="n">
         <v>122000</v>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="BV13" t="inlineStr">
         <is>
           <t>40,000</t>
         </is>

--- a/etf_holdings/2026-09-03_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-03_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV13"/>
+  <dimension ref="A1:CF13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,200 +589,250 @@
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>00403A_異動類型</t>
+          <t>00985A_異動類型</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>00403A_調整方向</t>
+          <t>00985A_調整方向</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>00403A_股票名稱_昨日</t>
+          <t>00985A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>00403A_股票名稱_今日</t>
+          <t>00985A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>00403A_權重_昨日</t>
+          <t>00985A_權重_昨日</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>00403A_權重_今日</t>
+          <t>00985A_權重_今日</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>00403A_權重變化</t>
+          <t>00985A_權重變化</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>00403A_股數_昨日</t>
+          <t>00985A_股數_昨日</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>00403A_股數_今日</t>
+          <t>00985A_股數_今日</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>00403A_股數變化</t>
+          <t>00985A_股數變化</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
+          <t>00992A_異動類型</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>00992A_調整方向</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>00992A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>00992A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>00992A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>00992A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>00992A_權重變化</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>00992A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>00992A_股數_今日</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>00992A_股數變化</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
           <t>00990A_異動類型</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>00990A_調整方向</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>00990A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>00990A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>00990A_權重_昨日</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>00990A_權重_今日</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>00990A_權重變化</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>00990A_股數_昨日</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>00990A_股數_今日</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>00990A_股數變化</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>00407A_異動類型</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>00407A_調整方向</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>00407A_權重_昨日</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>00407A_權重_今日</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>00407A_權重變化</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>00407A_股數_昨日</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>00407A_股數_今日</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>00407A_股數變化</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>00993A_異動類型</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>00993A_調整方向</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>00993A_權重_昨日</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>00993A_權重_今日</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>00993A_權重變化</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>00993A_股數_昨日</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>00993A_股數_今日</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>00993A_股數變化</t>
         </is>
@@ -800,11 +850,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00407A,00980A,00993A</t>
+          <t>00407A,00980A,00985A,00993A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -873,16 +923,52 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>緯穎科技服務</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>緯穎科技服務</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>4.11%</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>4.16%</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>56000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>167036</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>111,036</t>
+        </is>
+      </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
@@ -893,94 +979,104 @@
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr">
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>5.72%</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>5.87%</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>+0.15%</t>
         </is>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BT2" t="n">
         <v>195000</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BU2" t="n">
         <v>581644</v>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>386,644</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>3.49%</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>3.58%</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>+0.09%</t>
         </is>
       </c>
-      <c r="BT2" t="n">
+      <c r="CD2" t="n">
         <v>47000</v>
       </c>
-      <c r="BU2" t="n">
+      <c r="CE2" t="n">
         <v>140191</v>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>93,191</t>
         </is>
@@ -1119,48 +1215,58 @@
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr">
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>南電</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>南電</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>2.52%</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>2.17%</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>-0.35%</t>
         </is>
       </c>
-      <c r="BT3" t="n">
+      <c r="CD3" t="n">
         <v>216000</v>
       </c>
-      <c r="BU3" t="n">
+      <c r="CE3" t="n">
         <v>185000</v>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>-31,000</t>
         </is>
@@ -1169,12 +1275,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1182,7 +1288,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
+          <t>00992A,00993A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1225,118 +1331,128 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>1.02%</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>0.49%</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>-0.53%</t>
-        </is>
-      </c>
-      <c r="BJ4" t="n">
-        <v>2045000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>-1,045,000</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>7.61%</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>6.69%</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>235000</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>205000</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-30,000</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>1.69%</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>1.57%</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>-0.12%</t>
-        </is>
-      </c>
-      <c r="BT4" t="n">
-        <v>1338000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1276000</v>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>-62,000</t>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>4.04%</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>3.80%</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="CD4" t="n">
+        <v>30000</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>28000</v>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>-2,000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1344,55 +1460,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00981A,00993A</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.61%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.09%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-0.52%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>1457000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>219000</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-1,238,000</t>
-        </is>
-      </c>
+          <t>00407A,00993A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -1450,55 +1530,101 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="BT5" t="n">
-        <v>113000</v>
+        <v>2045000</v>
       </c>
       <c r="BU5" t="n">
-        <v>198000</v>
+        <v>1000000</v>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>-1,045,000</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="CD5" t="n">
+        <v>1338000</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>1276000</v>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>-62,000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1506,19 +1632,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00990A,00993A</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-0.52%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1457000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>219000</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-1,238,000</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -1549,52 +1711,16 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>0.70%</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1.28%</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>+0.58%</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1008000</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1665000</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>657,000</t>
-        </is>
-      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="inlineStr"/>
@@ -1605,62 +1731,72 @@
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr">
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>0.35%</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>+0.19%</t>
-        </is>
-      </c>
-      <c r="BT6" t="n">
-        <v>59000</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>131000</v>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>72,000</t>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2.28%</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>+0.96%</t>
+        </is>
+      </c>
+      <c r="CD6" t="n">
+        <v>113000</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>198000</v>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>85,000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1668,7 +1804,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
+          <t>00990A,00993A</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -1733,96 +1869,106 @@
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>55000</v>
+        <v>1008000</v>
       </c>
       <c r="BK7" t="n">
-        <v>80000</v>
+        <v>1665000</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>25,000</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
+          <t>657,000</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>大立光電</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>大立光電</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>0.94%</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>1.91%</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>+0.97%</t>
-        </is>
-      </c>
-      <c r="BT7" t="n">
-        <v>13000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>25000</v>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>12,000</t>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="CD7" t="n">
+        <v>59000</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>131000</v>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>72,000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1830,7 +1976,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00990A,00993A</t>
+          <t>00407A,00993A</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1873,33 +2019,15 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
+      <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1.49%</t>
-        </is>
-      </c>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="n">
-        <v>158000</v>
-      </c>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
@@ -1918,55 +2046,101 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="BT8" t="n">
-        <v>134000</v>
+        <v>55000</v>
       </c>
       <c r="BU8" t="n">
-        <v>107000</v>
+        <v>80000</v>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-27,000</t>
+          <t>25,000</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>+0.97%</t>
+        </is>
+      </c>
+      <c r="CD8" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>12,000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1974,7 +2148,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00982A,00993A</t>
+          <t>00990A,00993A</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -1997,52 +2171,16 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1.22%</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1.39%</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>+0.17%</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>3404000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3704000</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>300,000</t>
-        </is>
-      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
@@ -2063,72 +2201,100 @@
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
       <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
       <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr"/>
       <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
+      <c r="BK9" t="n">
+        <v>158000</v>
+      </c>
       <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr">
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>1.06%</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>1.70%</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>+0.64%</t>
-        </is>
-      </c>
-      <c r="BT9" t="n">
-        <v>611000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>939000</v>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>328,000</t>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>4.34%</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>-0.88%</t>
+        </is>
+      </c>
+      <c r="CD9" t="n">
+        <v>134000</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>107000</v>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>-27,000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2136,55 +2302,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00981A,00993A</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.90%</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.95%</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>2397000</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2427000</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>30,000</t>
-        </is>
-      </c>
+          <t>00982A,00993A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -2195,16 +2325,52 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1.39%</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>3404000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3704000</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>300,000</t>
+        </is>
+      </c>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
@@ -2235,62 +2401,72 @@
       <c r="BJ10" t="inlineStr"/>
       <c r="BK10" t="inlineStr"/>
       <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr">
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>1.62%</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>1.30%</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>-0.32%</t>
-        </is>
-      </c>
-      <c r="BT10" t="n">
-        <v>29000</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>23000</v>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>-6,000</t>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>+0.64%</t>
+        </is>
+      </c>
+      <c r="CD10" t="n">
+        <v>611000</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>939000</v>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>328,000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2298,19 +2474,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00990A,00993A</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4.90%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4.95%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2397000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2427000</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -2341,33 +2553,15 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
       <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
+      <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>0.60%</t>
-        </is>
-      </c>
+      <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="n">
-        <v>94000</v>
-      </c>
+      <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
@@ -2379,62 +2573,72 @@
       <c r="BJ11" t="inlineStr"/>
       <c r="BK11" t="inlineStr"/>
       <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="inlineStr">
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>1.98%</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>2.12%</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>+0.14%</t>
-        </is>
-      </c>
-      <c r="BT11" t="n">
-        <v>90000</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>100000</v>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>10,000</t>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="CD11" t="n">
+        <v>29000</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>23000</v>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>-6,000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2442,7 +2646,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00403A,00993A</t>
+          <t>00990A,00993A</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -2475,32 +2679,14 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="n">
-        <v>1000</v>
-      </c>
+      <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="inlineStr"/>
@@ -2513,60 +2699,88 @@
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
       <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr"/>
       <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="inlineStr"/>
+      <c r="BK12" t="n">
+        <v>94000</v>
+      </c>
       <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr">
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr"/>
+      <c r="BS12" t="inlineStr"/>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr"/>
+      <c r="BW12" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>0.87%</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>1.93%</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>+1.06%</t>
-        </is>
-      </c>
-      <c r="BT12" t="n">
-        <v>171000</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>390000</v>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>219,000</t>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2.12%</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="CD12" t="n">
+        <v>90000</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>100000</v>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -2639,94 +2853,104 @@
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr">
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BD13" t="inlineStr">
+      <c r="BN13" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BE13" t="inlineStr">
+      <c r="BO13" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="BP13" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
+      <c r="BQ13" t="inlineStr">
         <is>
           <t>0.98%</t>
         </is>
       </c>
-      <c r="BH13" t="inlineStr">
+      <c r="BR13" t="inlineStr">
         <is>
           <t>1.72%</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="BS13" t="inlineStr">
         <is>
           <t>+0.74%</t>
         </is>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BT13" t="n">
         <v>221000</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BU13" t="n">
         <v>351000</v>
       </c>
-      <c r="BL13" t="inlineStr">
+      <c r="BV13" t="inlineStr">
         <is>
           <t>130,000</t>
         </is>
       </c>
-      <c r="BM13" t="inlineStr">
+      <c r="BW13" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BX13" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="BY13" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
+      <c r="BZ13" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="BQ13" t="inlineStr">
+      <c r="CA13" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="BR13" t="inlineStr">
+      <c r="CB13" t="inlineStr">
         <is>
           <t>1.51%</t>
         </is>
       </c>
-      <c r="BS13" t="inlineStr">
+      <c r="CC13" t="inlineStr">
         <is>
           <t>+0.59%</t>
         </is>
       </c>
-      <c r="BT13" t="n">
+      <c r="CD13" t="n">
         <v>82000</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CE13" t="n">
         <v>122000</v>
       </c>
-      <c r="BV13" t="inlineStr">
+      <c r="CF13" t="inlineStr">
         <is>
           <t>40,000</t>
         </is>

--- a/etf_holdings/2026-09-03_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-03_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF13"/>
+  <dimension ref="A1:CP14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,250 +589,300 @@
       </c>
       <c r="AI1" t="inlineStr">
         <is>
+          <t>00403A_異動類型</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>00403A_調整方向</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>00403A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>00403A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>00403A_權重變化</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>00403A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>00403A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>00403A_股數變化</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
           <t>00985A_異動類型</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>00985A_調整方向</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>00985A_權重_昨日</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>00985A_權重_今日</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>00985A_權重變化</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>00985A_股數_昨日</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>00985A_股數_今日</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>00985A_股數變化</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>00992A_異動類型</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>00992A_調整方向</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>00992A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>00992A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>00992A_權重_昨日</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>00992A_權重_今日</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>00992A_權重變化</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>00992A_股數_昨日</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>00992A_股數_今日</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>00992A_股數變化</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>00990A_異動類型</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>00990A_調整方向</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>00990A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>00990A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>00990A_權重_昨日</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>00990A_權重_今日</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>00990A_權重變化</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>00990A_股數_昨日</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>00990A_股數_今日</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>00990A_股數變化</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>00407A_異動類型</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>00407A_調整方向</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>00407A_權重_昨日</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>00407A_權重_今日</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>00407A_權重變化</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>00407A_股數_昨日</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>00407A_股數_今日</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>00407A_股數變化</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>00993A_異動類型</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>00993A_調整方向</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>00993A_權重_昨日</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>00993A_權重_今日</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>00993A_權重變化</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>00993A_股數_昨日</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>00993A_股數_今日</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>00993A_股數變化</t>
         </is>
@@ -923,62 +973,62 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr">
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>緯穎科技服務</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>緯穎科技服務</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>4.11%</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>4.16%</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>+0.05%</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AZ2" t="n">
         <v>56000</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="BA2" t="n">
         <v>167036</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>111,036</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="inlineStr"/>
@@ -989,94 +1039,104 @@
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr">
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>5.72%</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>5.87%</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>+0.15%</t>
         </is>
       </c>
-      <c r="BT2" t="n">
+      <c r="CD2" t="n">
         <v>195000</v>
       </c>
-      <c r="BU2" t="n">
+      <c r="CE2" t="n">
         <v>581644</v>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>386,644</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>3.49%</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>3.58%</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>+0.09%</t>
         </is>
       </c>
-      <c r="CD2" t="n">
+      <c r="CN2" t="n">
         <v>47000</v>
       </c>
-      <c r="CE2" t="n">
+      <c r="CO2" t="n">
         <v>140191</v>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>93,191</t>
         </is>
@@ -1225,48 +1285,58 @@
       <c r="BT3" t="inlineStr"/>
       <c r="BU3" t="inlineStr"/>
       <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr">
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+      <c r="CD3" t="inlineStr"/>
+      <c r="CE3" t="inlineStr"/>
+      <c r="CF3" t="inlineStr"/>
+      <c r="CG3" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>南電</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>南電</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>2.52%</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>2.17%</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>-0.35%</t>
         </is>
       </c>
-      <c r="CD3" t="n">
+      <c r="CN3" t="n">
         <v>216000</v>
       </c>
-      <c r="CE3" t="n">
+      <c r="CO3" t="n">
         <v>185000</v>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>-31,000</t>
         </is>
@@ -1331,62 +1401,62 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr">
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AU4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>川湖</t>
         </is>
       </c>
-      <c r="AV4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>川湖</t>
         </is>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>7.61%</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>6.69%</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>-0.92%</t>
         </is>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BJ4" t="n">
         <v>235000</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BK4" t="n">
         <v>205000</v>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>-30,000</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="inlineStr"/>
@@ -1397,48 +1467,58 @@
       <c r="BT4" t="inlineStr"/>
       <c r="BU4" t="inlineStr"/>
       <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr">
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>川湖</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>川湖</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>4.04%</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>3.80%</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>-0.24%</t>
         </is>
       </c>
-      <c r="CD4" t="n">
+      <c r="CN4" t="n">
         <v>30000</v>
       </c>
-      <c r="CE4" t="n">
+      <c r="CO4" t="n">
         <v>28000</v>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>-2,000</t>
         </is>
@@ -1523,94 +1603,104 @@
       <c r="BJ5" t="inlineStr"/>
       <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr">
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>1.02%</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>0.49%</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>-0.53%</t>
         </is>
       </c>
-      <c r="BT5" t="n">
+      <c r="CD5" t="n">
         <v>2045000</v>
       </c>
-      <c r="BU5" t="n">
+      <c r="CE5" t="n">
         <v>1000000</v>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>-1,045,000</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>1.69%</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>1.57%</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>-0.12%</t>
         </is>
       </c>
-      <c r="CD5" t="n">
+      <c r="CN5" t="n">
         <v>1338000</v>
       </c>
-      <c r="CE5" t="n">
+      <c r="CO5" t="n">
         <v>1276000</v>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>-62,000</t>
         </is>
@@ -1741,48 +1831,58 @@
       <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr">
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
+      <c r="CG6" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>金像電子</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>金像電子</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>1.32%</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>2.28%</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>+0.96%</t>
         </is>
       </c>
-      <c r="CD6" t="n">
+      <c r="CN6" t="n">
         <v>113000</v>
       </c>
-      <c r="CE6" t="n">
+      <c r="CO6" t="n">
         <v>198000</v>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>85,000</t>
         </is>
@@ -1857,104 +1957,114 @@
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr">
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>京元電子</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>京元電子</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.70%</t>
         </is>
       </c>
-      <c r="BH7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>1.28%</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>+0.58%</t>
         </is>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BT7" t="n">
         <v>1008000</v>
       </c>
-      <c r="BK7" t="n">
+      <c r="BU7" t="n">
         <v>1665000</v>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>657,000</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
-      <c r="BR7" t="inlineStr"/>
-      <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
-      <c r="BW7" t="inlineStr">
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
+      <c r="CE7" t="inlineStr"/>
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>京元電子</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>京元電子</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>0.16%</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>0.35%</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>+0.19%</t>
         </is>
       </c>
-      <c r="CD7" t="n">
+      <c r="CN7" t="n">
         <v>59000</v>
       </c>
-      <c r="CE7" t="n">
+      <c r="CO7" t="n">
         <v>131000</v>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>72,000</t>
         </is>
@@ -2039,94 +2149,104 @@
       <c r="BJ8" t="inlineStr"/>
       <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr">
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>大立光</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>大立光</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>1.57%</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>+0.85%</t>
         </is>
       </c>
-      <c r="BT8" t="n">
+      <c r="CD8" t="n">
         <v>55000</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CE8" t="n">
         <v>80000</v>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>25,000</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>大立光電</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>大立光電</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>0.94%</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>1.91%</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>+0.97%</t>
         </is>
       </c>
-      <c r="CD8" t="n">
+      <c r="CN8" t="n">
         <v>13000</v>
       </c>
-      <c r="CE8" t="n">
+      <c r="CO8" t="n">
         <v>25000</v>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>12,000</t>
         </is>
@@ -2201,86 +2321,96 @@
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
+      <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>1.49%</t>
-        </is>
-      </c>
+      <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr"/>
       <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="n">
-        <v>158000</v>
-      </c>
+      <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
       <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
       <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
       <c r="BS9" t="inlineStr"/>
       <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
+      <c r="BU9" t="n">
+        <v>158000</v>
+      </c>
       <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr">
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>奇鋐</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>奇鋐</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>4.34%</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>3.46%</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>-0.88%</t>
         </is>
       </c>
-      <c r="CD9" t="n">
+      <c r="CN9" t="n">
         <v>134000</v>
       </c>
-      <c r="CE9" t="n">
+      <c r="CO9" t="n">
         <v>107000</v>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>-27,000</t>
         </is>
@@ -2411,48 +2541,58 @@
       <c r="BT10" t="inlineStr"/>
       <c r="BU10" t="inlineStr"/>
       <c r="BV10" t="inlineStr"/>
-      <c r="BW10" t="inlineStr">
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="inlineStr"/>
+      <c r="CF10" t="inlineStr"/>
+      <c r="CG10" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>緯創</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>緯創</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>1.06%</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>1.70%</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>+0.64%</t>
         </is>
       </c>
-      <c r="CD10" t="n">
+      <c r="CN10" t="n">
         <v>611000</v>
       </c>
-      <c r="CE10" t="n">
+      <c r="CO10" t="n">
         <v>939000</v>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>328,000</t>
         </is>
@@ -2583,48 +2723,58 @@
       <c r="BT11" t="inlineStr"/>
       <c r="BU11" t="inlineStr"/>
       <c r="BV11" t="inlineStr"/>
-      <c r="BW11" t="inlineStr">
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr"/>
+      <c r="CC11" t="inlineStr"/>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>健策</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>健策</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>1.62%</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>1.30%</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>-0.32%</t>
         </is>
       </c>
-      <c r="CD11" t="n">
+      <c r="CN11" t="n">
         <v>29000</v>
       </c>
-      <c r="CE11" t="n">
+      <c r="CO11" t="n">
         <v>23000</v>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>-6,000</t>
         </is>
@@ -2699,86 +2849,96 @@
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
       <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
+      <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>0.60%</t>
-        </is>
-      </c>
+      <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr"/>
       <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="n">
-        <v>94000</v>
-      </c>
+      <c r="BK12" t="inlineStr"/>
       <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
       <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
       <c r="BQ12" t="inlineStr"/>
-      <c r="BR12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
       <c r="BS12" t="inlineStr"/>
       <c r="BT12" t="inlineStr"/>
-      <c r="BU12" t="inlineStr"/>
+      <c r="BU12" t="n">
+        <v>94000</v>
+      </c>
       <c r="BV12" t="inlineStr"/>
-      <c r="BW12" t="inlineStr">
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="inlineStr"/>
+      <c r="CA12" t="inlineStr"/>
+      <c r="CB12" t="inlineStr"/>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr"/>
+      <c r="CE12" t="inlineStr"/>
+      <c r="CF12" t="inlineStr"/>
+      <c r="CG12" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>貿聯-KY</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>貿聯-KY</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>1.98%</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>2.12%</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>+0.14%</t>
         </is>
       </c>
-      <c r="CD12" t="n">
+      <c r="CN12" t="n">
         <v>90000</v>
       </c>
-      <c r="CE12" t="n">
+      <c r="CO12" t="n">
         <v>100000</v>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>10,000</t>
         </is>
@@ -2787,12 +2947,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2800,7 +2960,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
+          <t>00403A,00993A</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -2833,14 +2993,32 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
       <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
+      <c r="AP13" t="n">
+        <v>1000</v>
+      </c>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="inlineStr"/>
@@ -2863,94 +3041,250 @@
       <c r="BJ13" t="inlineStr"/>
       <c r="BK13" t="inlineStr"/>
       <c r="BL13" t="inlineStr"/>
-      <c r="BM13" t="inlineStr">
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr"/>
+      <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr"/>
+      <c r="CF13" t="inlineStr"/>
+      <c r="CG13" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="CH13" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="CK13" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="CL13" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="CM13" t="inlineStr">
+        <is>
+          <t>+1.06%</t>
+        </is>
+      </c>
+      <c r="CN13" t="n">
+        <v>171000</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>390000</v>
+      </c>
+      <c r="CP13" t="inlineStr">
+        <is>
+          <t>219,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00407A,00993A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr"/>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="BQ13" t="inlineStr">
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
         <is>
           <t>0.98%</t>
         </is>
       </c>
-      <c r="BR13" t="inlineStr">
+      <c r="CB14" t="inlineStr">
         <is>
           <t>1.72%</t>
         </is>
       </c>
-      <c r="BS13" t="inlineStr">
+      <c r="CC14" t="inlineStr">
         <is>
           <t>+0.74%</t>
         </is>
       </c>
-      <c r="BT13" t="n">
+      <c r="CD14" t="n">
         <v>221000</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CE14" t="n">
         <v>351000</v>
       </c>
-      <c r="BV13" t="inlineStr">
+      <c r="CF14" t="inlineStr">
         <is>
           <t>130,000</t>
         </is>
       </c>
-      <c r="BW13" t="inlineStr">
+      <c r="CG14" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BX13" t="inlineStr">
+      <c r="CH14" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BY13" t="inlineStr">
+      <c r="CI14" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="BZ13" t="inlineStr">
+      <c r="CJ14" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="CA13" t="inlineStr">
+      <c r="CK14" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="CB13" t="inlineStr">
+      <c r="CL14" t="inlineStr">
         <is>
           <t>1.51%</t>
         </is>
       </c>
-      <c r="CC13" t="inlineStr">
+      <c r="CM14" t="inlineStr">
         <is>
           <t>+0.59%</t>
         </is>
       </c>
-      <c r="CD13" t="n">
+      <c r="CN14" t="n">
         <v>82000</v>
       </c>
-      <c r="CE13" t="n">
+      <c r="CO14" t="n">
         <v>122000</v>
       </c>
-      <c r="CF13" t="inlineStr">
+      <c r="CP14" t="inlineStr">
         <is>
           <t>40,000</t>
         </is>
